--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/KANSAS_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/KANSAS_2013.xlsx
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C112">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C158">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C191">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C538">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C588">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C876">
